--- a/model/foragingModelTable.xlsx
+++ b/model/foragingModelTable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exs165/Dropbox/foraging/code/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exs165/Dropbox/foraging/stochastic-mvt-project/model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434D1C92-4E2F-5241-8F27-B17FA0246812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C848007-5036-2849-BF4A-D392C6542052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="460" yWindow="500" windowWidth="27240" windowHeight="16320" xr2:uid="{AF09A64C-08B3-A642-B0D0-C38CF1EBFD20}"/>
   </bookViews>
@@ -669,7 +669,7 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -729,7 +729,7 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -789,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -849,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -909,7 +909,7 @@
         <v>0</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -969,7 +969,7 @@
         <v>0</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26">
         <v>0</v>

--- a/model/foragingModelTable.xlsx
+++ b/model/foragingModelTable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exs165/Dropbox/foraging/stochastic-mvt-project/model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C848007-5036-2849-BF4A-D392C6542052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1487CA-6407-5241-BF6B-4E556C624CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="460" yWindow="500" windowWidth="27240" windowHeight="16320" xr2:uid="{AF09A64C-08B3-A642-B0D0-C38CF1EBFD20}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="22">
   <si>
     <t>softmax</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>twoScalar</t>
+  </si>
+  <si>
+    <t>bias</t>
   </si>
 </sst>
 </file>
@@ -458,10 +461,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766F6688-A436-6A43-9B8F-A83A43AD55B0}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -480,8 +483,11 @@
       <c r="F1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -500,8 +506,11 @@
       <c r="F2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -520,8 +529,11 @@
       <c r="F3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -540,8 +552,11 @@
       <c r="F4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -560,8 +575,11 @@
       <c r="F5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -578,10 +596,13 @@
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -598,10 +619,13 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -618,10 +642,13 @@
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -640,8 +667,11 @@
       <c r="F9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -660,8 +690,11 @@
       <c r="F10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -680,8 +713,11 @@
       <c r="F11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -700,8 +736,11 @@
       <c r="F12" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -720,8 +759,11 @@
       <c r="F13" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -740,8 +782,11 @@
       <c r="F14" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -760,8 +805,11 @@
       <c r="F15" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -780,8 +828,11 @@
       <c r="F16" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -800,8 +851,11 @@
       <c r="F17" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -820,8 +874,11 @@
       <c r="F18" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -840,8 +897,11 @@
       <c r="F19" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -860,8 +920,11 @@
       <c r="F20" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -880,8 +943,11 @@
       <c r="F21" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -900,8 +966,11 @@
       <c r="F22" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -920,8 +989,11 @@
       <c r="F23" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -940,8 +1012,11 @@
       <c r="F24" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -960,8 +1035,11 @@
       <c r="F25" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -979,6 +1057,9 @@
       </c>
       <c r="F26" t="s">
         <v>8</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/model/foragingModelTable.xlsx
+++ b/model/foragingModelTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exs165/Dropbox/foraging/stochastic-mvt-project/model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1487CA-6407-5241-BF6B-4E556C624CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFAAE508-4FFC-8D42-BBE0-583B015EB163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="460" yWindow="500" windowWidth="27240" windowHeight="16320" xr2:uid="{AF09A64C-08B3-A642-B0D0-C38CF1EBFD20}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="22">
   <si>
     <t>softmax</t>
   </si>
@@ -461,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766F6688-A436-6A43-9B8F-A83A43AD55B0}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -1062,6 +1062,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" t="s">
+        <v>7</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/model/foragingModelTable.xlsx
+++ b/model/foragingModelTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exs165/Dropbox/foraging/stochastic-mvt-project/model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFAAE508-4FFC-8D42-BBE0-583B015EB163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983B83BD-D7CF-5042-AC55-2BC79D21AC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="460" yWindow="500" windowWidth="27240" windowHeight="16320" xr2:uid="{AF09A64C-08B3-A642-B0D0-C38CF1EBFD20}"/>
+    <workbookView xWindow="-28800" yWindow="4100" windowWidth="28800" windowHeight="17500" xr2:uid="{AF09A64C-08B3-A642-B0D0-C38CF1EBFD20}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="24">
   <si>
     <t>softmax</t>
   </si>
@@ -47,9 +47,6 @@
     <t>epsilon-softmax</t>
   </si>
   <si>
-    <t>fit</t>
-  </si>
-  <si>
     <t>twoExponential</t>
   </si>
   <si>
@@ -102,6 +99,15 @@
   </si>
   <si>
     <t>bias</t>
+  </si>
+  <si>
+    <t>separate</t>
+  </si>
+  <si>
+    <t>single</t>
+  </si>
+  <si>
+    <t>null</t>
   </si>
 </sst>
 </file>
@@ -165,9 +171,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -205,7 +211,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -311,7 +317,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -453,7 +459,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -461,30 +467,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766F6688-A436-6A43-9B8F-A83A43AD55B0}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
       <c r="F1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -501,13 +507,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -515,22 +521,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
         <v>13</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
+      <c r="G3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -547,13 +553,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -570,13 +576,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -593,13 +599,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="G6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -616,13 +622,13 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="G7" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -639,13 +645,13 @@
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="G8" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -662,13 +668,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="G9" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -685,13 +691,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="G10" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -708,13 +714,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="G11" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -731,13 +737,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" t="s">
         <v>5</v>
       </c>
-      <c r="F12" t="s">
-        <v>6</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
+      <c r="G12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -754,13 +760,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="G13" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -777,13 +783,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="G14" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -800,13 +806,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="G15" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -823,13 +829,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="G16" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -846,13 +852,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="G17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -869,13 +875,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>6</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="G18" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -892,13 +898,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="G19" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -915,13 +921,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="G20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -938,13 +944,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="G21" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -961,13 +967,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>7</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="G22" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -984,13 +990,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>8</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="G23" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -1007,13 +1013,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F24" t="s">
-        <v>6</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="G24" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -1030,13 +1036,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F25" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="G25" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -1053,13 +1059,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F26" t="s">
-        <v>8</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="G26" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -1076,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="G27" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -1099,13 +1105,36 @@
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F28" t="s">
-        <v>7</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="G28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/model/foragingModelTable.xlsx
+++ b/model/foragingModelTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exs165/Dropbox/foraging/stochastic-mvt-project/model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983B83BD-D7CF-5042-AC55-2BC79D21AC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C100035-6BCB-CF46-A4CF-67A5C7CBFC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28800" yWindow="4100" windowWidth="28800" windowHeight="17500" xr2:uid="{AF09A64C-08B3-A642-B0D0-C38CF1EBFD20}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="24">
   <si>
     <t>softmax</t>
   </si>
@@ -467,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766F6688-A436-6A43-9B8F-A83A43AD55B0}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -1137,6 +1137,29 @@
         <v>21</v>
       </c>
     </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/model/foragingModelTable.xlsx
+++ b/model/foragingModelTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exs165/Dropbox/foraging/stochastic-mvt-project/model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C100035-6BCB-CF46-A4CF-67A5C7CBFC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C06858F-8C9B-984A-9453-219175C0EDE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="4100" windowWidth="28800" windowHeight="17500" xr2:uid="{AF09A64C-08B3-A642-B0D0-C38CF1EBFD20}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" xr2:uid="{AF09A64C-08B3-A642-B0D0-C38CF1EBFD20}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,17 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="21">
   <si>
     <t>softmax</t>
   </si>
   <si>
-    <t>epsilon-greedy</t>
-  </si>
-  <si>
-    <t>epsilon-softmax</t>
-  </si>
-  <si>
     <t>twoExponential</t>
   </si>
   <si>
@@ -72,9 +66,6 @@
   </si>
   <si>
     <t>betaFunction</t>
-  </si>
-  <si>
-    <t>deterministic</t>
   </si>
   <si>
     <t>none</t>
@@ -467,30 +458,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766F6688-A436-6A43-9B8F-A83A43AD55B0}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" t="s">
-        <v>14</v>
-      </c>
       <c r="G1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -507,21 +498,21 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>12</v>
+      <c r="B3" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -530,21 +521,21 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>1</v>
+      <c r="B4" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -553,21 +544,21 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>2</v>
+      <c r="B5" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -576,13 +567,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -593,19 +584,19 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -616,19 +607,19 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -642,16 +633,16 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -662,19 +653,19 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
         <v>5</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -691,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -708,19 +699,19 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -731,19 +722,19 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
       </c>
       <c r="G12" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -760,13 +751,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -777,19 +768,19 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s">
         <v>4</v>
       </c>
-      <c r="F14" t="s">
-        <v>7</v>
-      </c>
       <c r="G14" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -800,19 +791,19 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F15" t="s">
         <v>5</v>
       </c>
       <c r="G15" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -832,10 +823,10 @@
         <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G16" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -846,7 +837,7 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -855,10 +846,10 @@
         <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G17" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -869,19 +860,19 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F18" t="s">
         <v>5</v>
       </c>
       <c r="G18" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -898,13 +889,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G19" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -915,19 +906,19 @@
         <v>0</v>
       </c>
       <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20" t="s">
         <v>1</v>
       </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20" t="s">
-        <v>19</v>
-      </c>
       <c r="F20" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -938,19 +929,19 @@
         <v>0</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" t="s">
         <v>5</v>
       </c>
       <c r="G21" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -967,13 +958,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" t="s">
         <v>3</v>
       </c>
-      <c r="F22" t="s">
-        <v>6</v>
-      </c>
       <c r="G22" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -984,19 +975,19 @@
         <v>0</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F23" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G23" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -1007,157 +998,19 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F24" t="s">
         <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" t="s">
-        <v>6</v>
-      </c>
-      <c r="G25" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" t="s">
-        <v>7</v>
-      </c>
-      <c r="G26" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-      <c r="E30" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/model/foragingModelTable.xlsx
+++ b/model/foragingModelTable.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exs165/Dropbox/foraging/stochastic-mvt-project/model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C06858F-8C9B-984A-9453-219175C0EDE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1887B2D-6A71-A24C-BADC-F5CF4CE275AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" xr2:uid="{AF09A64C-08B3-A642-B0D0-C38CF1EBFD20}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,14 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="18">
   <si>
     <t>softmax</t>
   </si>
   <si>
-    <t>twoExponential</t>
-  </si>
-  <si>
     <t>exponential</t>
   </si>
   <si>
@@ -80,13 +77,7 @@
     <t>hyperbolic</t>
   </si>
   <si>
-    <t>twoHyperbolic</t>
-  </si>
-  <si>
     <t>scalar</t>
-  </si>
-  <si>
-    <t>twoScalar</t>
   </si>
   <si>
     <t>bias</t>
@@ -458,30 +449,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766F6688-A436-6A43-9B8F-A83A43AD55B0}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" t="s">
-        <v>9</v>
-      </c>
       <c r="F1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -498,13 +489,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -521,13 +512,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -544,13 +535,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -567,13 +558,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -590,13 +581,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -613,13 +604,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -636,13 +627,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -659,13 +650,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -682,13 +673,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
         <v>2</v>
       </c>
-      <c r="F10" t="s">
-        <v>3</v>
-      </c>
       <c r="G10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -705,13 +696,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -728,13 +719,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -751,13 +742,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -774,13 +765,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -797,220 +788,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" t="s">
-        <v>3</v>
-      </c>
-      <c r="G16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" t="s">
-        <v>4</v>
-      </c>
-      <c r="G17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18" t="s">
-        <v>16</v>
-      </c>
-      <c r="F18" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" t="s">
-        <v>3</v>
-      </c>
-      <c r="G19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21" t="s">
-        <v>1</v>
-      </c>
-      <c r="F21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/model/foragingModelTable.xlsx
+++ b/model/foragingModelTable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exs165/Dropbox/foraging/stochastic-mvt-project/model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exs165/Dropbox/foraging/foraging_variability/model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1887B2D-6A71-A24C-BADC-F5CF4CE275AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6245CD-DA3C-2744-ACB0-631D70A61EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" xr2:uid="{AF09A64C-08B3-A642-B0D0-C38CF1EBFD20}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="18">
   <si>
     <t>softmax</t>
   </si>
@@ -50,9 +50,6 @@
     <t>block</t>
   </si>
   <si>
-    <t>rw</t>
-  </si>
-  <si>
     <t>modelNumber</t>
   </si>
   <si>
@@ -65,12 +62,6 @@
     <t>betaFunction</t>
   </si>
   <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t>rhoFunction</t>
-  </si>
-  <si>
     <t>learnRho</t>
   </si>
   <si>
@@ -90,6 +81,15 @@
   </si>
   <si>
     <t>null</t>
+  </si>
+  <si>
+    <t>scalar_exp</t>
+  </si>
+  <si>
+    <t>startRho</t>
+  </si>
+  <si>
+    <t>continuous</t>
   </si>
 </sst>
 </file>
@@ -449,30 +449,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766F6688-A436-6A43-9B8F-A83A43AD55B0}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s">
         <v>11</v>
-      </c>
-      <c r="D1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -489,13 +489,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -512,13 +512,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -535,13 +535,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -558,13 +558,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -581,13 +581,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -604,13 +604,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -627,13 +627,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>3</v>
       </c>
       <c r="G8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -650,13 +650,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -679,7 +679,7 @@
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -702,7 +702,7 @@
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -722,10 +722,10 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -742,13 +742,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -765,13 +765,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
         <v>3</v>
       </c>
       <c r="G14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -788,16 +788,112 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
         <v>12</v>
       </c>
-      <c r="F15" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" t="s">
-        <v>16</v>
-      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B20" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>